--- a/backend/data/financials_by_company/1CLNX.MI.xlsx
+++ b/backend/data/financials_by_company/1CLNX.MI.xlsx
@@ -4278,10 +4278,8 @@
           <t>Madrid</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>28007</t>
-        </is>
+      <c r="C2" t="n">
+        <v>28007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
